--- a/paper/data/merapi_liq.xlsx
+++ b/paper/data/merapi_liq.xlsx
@@ -1,60 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743AB197-80CD-44D4-B33D-73946CB2C939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB21EE6-C465-43F1-8657-1FE07DB998F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="4280" windowWidth="22260" windowHeight="9770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3470" yWindow="3080" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="44">
-  <si>
-    <t xml:space="preserve">   SiO2  </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="50">
   <si>
     <t xml:space="preserve">   Al2O3 </t>
   </si>
   <si>
-    <t xml:space="preserve">   FeO   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   MnO   </t>
-  </si>
-  <si>
     <t xml:space="preserve">   TiO2  </t>
   </si>
   <si>
-    <t xml:space="preserve">   Na2O  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   MgO   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   F     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   CaO   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Cl    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   K2O   </t>
-  </si>
-  <si>
     <t xml:space="preserve">  Total  </t>
   </si>
   <si>
@@ -130,18 +114,74 @@
     <t>MER061506-L</t>
   </si>
   <si>
+    <t xml:space="preserve">06_matrix1_g3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_matrix1_g4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_matrix1_g5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_matrix1_g6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_matrix1_g7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_matrix1_g8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_matrix1_g10 </t>
+  </si>
+  <si>
+    <t>M98-031</t>
+  </si>
+  <si>
+    <t>HPS</t>
+  </si>
+  <si>
+    <t>GERTISSER &amp; KELLER, 2003</t>
+  </si>
+  <si>
+    <t>M97-068</t>
+  </si>
+  <si>
+    <t>M96-102</t>
+  </si>
+  <si>
+    <t>M96-164</t>
+  </si>
+  <si>
+    <t>SiO2</t>
+  </si>
+  <si>
+    <t>FeO</t>
+  </si>
+  <si>
+    <t>MnO</t>
+  </si>
+  <si>
+    <t>MgO</t>
+  </si>
+  <si>
+    <t>CaO</t>
+  </si>
+  <si>
+    <t>Na2O</t>
+  </si>
+  <si>
+    <t>K2O</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Cl</t>
+  </si>
+  <si>
     <r>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
+      <t>P2</t>
     </r>
     <r>
       <rPr>
@@ -151,39 +191,8 @@
         <family val="1"/>
         <scheme val="minor"/>
       </rPr>
-      <t>O</t>
+      <t>O5</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">06_matrix1_g3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">06_matrix1_g4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">06_matrix1_g5 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">06_matrix1_g6 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">06_matrix1_g7 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">06_matrix1_g8 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">06_matrix1_g10 </t>
   </si>
 </sst>
 </file>
@@ -199,17 +208,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="1"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="1"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -239,9 +249,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.81640625" customWidth="1"/>
@@ -565,69 +591,69 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" t="s">
-        <v>28</v>
-      </c>
       <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
       <c r="H1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" t="s">
         <v>2</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>2010</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>55.8</v>
@@ -665,16 +691,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>2010</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>55.4</v>
@@ -712,16 +738,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>2010</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>55.5</v>
@@ -759,16 +785,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>2010</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>54.9</v>
@@ -806,16 +832,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>2010</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>54.9</v>
@@ -853,16 +879,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>2010</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>55</v>
@@ -900,16 +926,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B8">
         <v>2010</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E8">
         <v>68.932000000000002</v>
@@ -950,16 +976,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>2010</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E9">
         <v>67.370999999999995</v>
@@ -1000,16 +1026,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>2010</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E10">
         <v>69.173000000000002</v>
@@ -1050,16 +1076,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B11">
         <v>2010</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E11">
         <v>68.697000000000003</v>
@@ -1100,16 +1126,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>2010</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E12">
         <v>68.489000000000004</v>
@@ -1150,16 +1176,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>2010</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E13">
         <v>67.597999999999999</v>
@@ -1200,16 +1226,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B14">
         <v>2010</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E14">
         <v>68.051000000000002</v>
@@ -1250,16 +1276,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>2006</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E15" s="1">
         <v>70.022000000000006</v>
@@ -1300,16 +1326,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>2006</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1">
         <v>70.643000000000001</v>
@@ -1348,18 +1374,18 @@
         <v>98.549000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>2006</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1">
         <v>70.822999999999993</v>
@@ -1398,18 +1424,18 @@
         <v>98.697000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>2006</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1">
         <v>70.084000000000003</v>
@@ -1447,19 +1473,33 @@
       <c r="Q18" s="1">
         <v>98.88</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S18" s="2"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
+      <c r="AB18" s="4"/>
+      <c r="AC18" s="4"/>
+      <c r="AD18" s="4"/>
+      <c r="AE18" s="4"/>
+      <c r="AF18" s="4"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B19">
         <v>2006</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E19" s="1">
         <v>71.567999999999998</v>
@@ -1497,19 +1537,33 @@
       <c r="Q19" s="1">
         <v>99.393000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S19" s="5"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B20">
         <v>2006</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E20" s="1">
         <v>70.158000000000001</v>
@@ -1547,19 +1601,33 @@
       <c r="Q20" s="1">
         <v>98.418000000000006</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S20" s="5"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B21">
         <v>2006</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E21" s="1">
         <v>70.587999999999994</v>
@@ -1597,19 +1665,33 @@
       <c r="Q21" s="1">
         <v>98.641000000000005</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S21" s="5"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>2006</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E22">
         <v>55.7</v>
@@ -1644,19 +1726,33 @@
       <c r="Q22">
         <v>99.8</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S22" s="5"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>2006</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E23">
         <v>55.9</v>
@@ -1691,53 +1787,299 @@
       <c r="Q23">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S23" s="5"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>2006</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24">
+        <v>20</v>
+      </c>
+      <c r="E24" s="6">
         <v>55.4</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="6">
         <v>0.77</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="6">
         <v>19.079999999999998</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="6">
         <v>7.77</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="6">
         <v>0.2</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="6">
         <v>2.48</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="6">
         <v>8.33</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="6">
         <v>3.47</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="6">
         <v>2.14</v>
       </c>
-      <c r="P24">
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6">
         <v>0.38</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="6">
         <v>100</v>
       </c>
+      <c r="S24" s="5"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="7">
+        <v>51.7</v>
+      </c>
+      <c r="F25" s="7">
+        <v>0.84</v>
+      </c>
+      <c r="G25" s="7">
+        <v>18.77</v>
+      </c>
+      <c r="H25" s="7">
+        <v>7.5403240000000009</v>
+      </c>
+      <c r="I25" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="J25" s="7">
+        <v>3.09</v>
+      </c>
+      <c r="K25" s="7">
+        <v>9.23</v>
+      </c>
+      <c r="L25" s="7">
+        <v>3.35</v>
+      </c>
+      <c r="M25" s="7">
+        <v>1.9</v>
+      </c>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="7">
+        <v>0.26</v>
+      </c>
+      <c r="Q25" s="7"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="7">
+        <v>51.85</v>
+      </c>
+      <c r="F26" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="G26" s="7">
+        <v>18.53</v>
+      </c>
+      <c r="H26" s="7">
+        <v>8.6830700000000007</v>
+      </c>
+      <c r="I26" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="J26" s="7">
+        <v>3.9</v>
+      </c>
+      <c r="K26" s="7">
+        <v>9.58</v>
+      </c>
+      <c r="L26" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="M26" s="7">
+        <v>1.98</v>
+      </c>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="Q26" s="7"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="7">
+        <v>51.87</v>
+      </c>
+      <c r="F27" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="G27" s="7">
+        <v>20.440000000000001</v>
+      </c>
+      <c r="H27" s="7">
+        <v>7.4143520000000009</v>
+      </c>
+      <c r="I27" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="J27" s="7">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="K27" s="7">
+        <v>8.86</v>
+      </c>
+      <c r="L27" s="7">
+        <v>3.35</v>
+      </c>
+      <c r="M27" s="7">
+        <v>1.74</v>
+      </c>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="7">
+        <v>0.31</v>
+      </c>
+      <c r="Q27" s="7"/>
+      <c r="T27" s="3"/>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="7">
+        <v>51.86</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0.84</v>
+      </c>
+      <c r="G28" s="7">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="H28" s="7">
+        <v>7.6303040000000006</v>
+      </c>
+      <c r="I28" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="J28" s="7">
+        <v>3.02</v>
+      </c>
+      <c r="K28" s="7">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="L28" s="7">
+        <v>3.36</v>
+      </c>
+      <c r="M28" s="7">
+        <v>1.82</v>
+      </c>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="Q28" s="7"/>
+      <c r="T28" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/paper/data/merapi_liq.xlsx
+++ b/paper/data/merapi_liq.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB21EE6-C465-43F1-8657-1FE07DB998F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B07AC94-A2DD-4105-B42D-4E3D14371270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3470" yWindow="3080" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,9 +138,6 @@
     <t>M98-031</t>
   </si>
   <si>
-    <t>HPS</t>
-  </si>
-  <si>
     <t>GERTISSER &amp; KELLER, 2003</t>
   </si>
   <si>
@@ -193,6 +190,9 @@
       </rPr>
       <t>O5</t>
     </r>
+  </si>
+  <si>
+    <t>pre-2006</t>
   </si>
 </sst>
 </file>
@@ -603,7 +603,7 @@
         <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
@@ -612,31 +612,31 @@
         <v>0</v>
       </c>
       <c r="H1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>43</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>44</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>45</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>46</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>47</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>48</v>
-      </c>
-      <c r="P1" t="s">
-        <v>49</v>
       </c>
       <c r="Q1" t="s">
         <v>2</v>
@@ -1870,10 +1870,10 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
         <v>35</v>
-      </c>
-      <c r="C25" t="s">
-        <v>36</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>
@@ -1927,13 +1927,13 @@
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
         <v>35</v>
-      </c>
-      <c r="C26" t="s">
-        <v>36</v>
       </c>
       <c r="D26" t="s">
         <v>20</v>
@@ -1987,13 +1987,13 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
         <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>36</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
         <v>35</v>
-      </c>
-      <c r="C28" t="s">
-        <v>36</v>
       </c>
       <c r="D28" t="s">
         <v>20</v>

--- a/paper/data/merapi_liq.xlsx
+++ b/paper/data/merapi_liq.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B07AC94-A2DD-4105-B42D-4E3D14371270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99394154-AFC7-4513-8EDA-697C2640E311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3470" yWindow="3080" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14920" yWindow="9350" windowWidth="23300" windowHeight="11180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1910,7 +1910,9 @@
       <c r="P25" s="7">
         <v>0.26</v>
       </c>
-      <c r="Q25" s="7"/>
+      <c r="Q25" s="7">
+        <v>100.21</v>
+      </c>
       <c r="S25" s="5"/>
       <c r="T25" s="3"/>
       <c r="V25" s="3"/>
@@ -1970,7 +1972,9 @@
       <c r="P26" s="7">
         <v>0.28999999999999998</v>
       </c>
-      <c r="Q26" s="7"/>
+      <c r="Q26" s="7">
+        <v>100.36</v>
+      </c>
       <c r="S26" s="5"/>
       <c r="T26" s="3"/>
       <c r="V26" s="3"/>
@@ -2030,7 +2034,9 @@
       <c r="P27" s="7">
         <v>0.31</v>
       </c>
-      <c r="Q27" s="7"/>
+      <c r="Q27" s="7">
+        <v>99.91</v>
+      </c>
       <c r="T27" s="3"/>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.35">
@@ -2078,7 +2084,9 @@
       <c r="P28" s="7">
         <v>0.28999999999999998</v>
       </c>
-      <c r="Q28" s="7"/>
+      <c r="Q28" s="7">
+        <v>99.93</v>
+      </c>
       <c r="T28" s="3"/>
     </row>
   </sheetData>
